--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9558" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9559" uniqueCount="876">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,6 +656,14 @@
   </si>
   <si>
     <t>Version du document</t>
+  </si>
+  <si>
+    <t>R5: `Composition.version` (new:string)</t>
+  </si>
+  <si>
+    <t>Element `Composition.version` has a context of Composition based on following the parent source element upwards and mapping to `Composition`.
+Element `Composition.version` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+While each resource, including the composition itself, has its own version identifier, this is a formal identifier for the logical version of the Composition as a whole. It would remain constant if the resources were moved to a new server, and all got new individual resource versions, for example.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -5237,9 +5245,11 @@
         <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -5297,10 +5307,10 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -5320,19 +5330,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>79</v>
@@ -5350,13 +5360,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5416,7 +5426,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>120</v>
@@ -5439,10 +5449,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5554,10 +5564,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5565,7 +5575,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>80</v>
@@ -5669,13 +5679,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="B23" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="C23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -5700,7 +5710,7 @@
         <v>112</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>198</v>
@@ -5786,10 +5796,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5901,10 +5911,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6016,10 +6026,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6045,13 +6055,13 @@
         <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6059,7 +6069,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>78</v>
@@ -6101,7 +6111,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -6133,10 +6143,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6159,13 +6169,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6204,17 +6214,17 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -6246,13 +6256,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>78</v>
@@ -6274,13 +6284,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6292,7 +6302,7 @@
         <v>78</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>78</v>
@@ -6331,7 +6341,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -6363,13 +6373,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
@@ -6394,7 +6404,7 @@
         <v>112</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>198</v>
@@ -6480,10 +6490,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6595,10 +6605,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6710,10 +6720,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6739,13 +6749,13 @@
         <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6753,7 +6763,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6795,7 +6805,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>91</v>
@@ -6827,10 +6837,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6853,13 +6863,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6890,7 +6900,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6918,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6940,13 +6950,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6971,7 +6981,7 @@
         <v>112</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>198</v>
@@ -7057,10 +7067,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7172,10 +7182,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7287,10 +7297,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7316,13 +7326,13 @@
         <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -7330,7 +7340,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -7372,7 +7382,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -7404,10 +7414,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7430,13 +7440,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7487,7 +7497,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7519,13 +7529,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7550,7 +7560,7 @@
         <v>112</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>198</v>
@@ -7636,10 +7646,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7751,10 +7761,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7866,10 +7876,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7895,13 +7905,13 @@
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7909,7 +7919,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>78</v>
@@ -7951,7 +7961,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>91</v>
@@ -7983,10 +7993,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8009,13 +8019,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8066,7 +8076,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -8098,10 +8108,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8127,13 +8137,13 @@
         <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8141,7 +8151,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>78</v>
@@ -8183,7 +8193,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>91</v>
@@ -8215,10 +8225,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8241,13 +8251,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8298,7 +8308,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8330,19 +8340,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>79</v>
@@ -8360,13 +8370,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8426,7 +8436,7 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>120</v>
@@ -8449,10 +8459,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8564,10 +8574,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8575,7 +8585,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>80</v>
@@ -8679,13 +8689,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -8710,7 +8720,7 @@
         <v>112</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>198</v>
@@ -8796,10 +8806,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8911,10 +8921,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9026,10 +9036,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9055,13 +9065,13 @@
         <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9069,7 +9079,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>78</v>
@@ -9111,7 +9121,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>91</v>
@@ -9143,10 +9153,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9169,13 +9179,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9214,17 +9224,17 @@
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9256,13 +9266,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -9284,13 +9294,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9302,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -9341,7 +9351,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9373,13 +9383,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -9404,7 +9414,7 @@
         <v>112</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>198</v>
@@ -9490,10 +9500,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9605,10 +9615,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9720,10 +9730,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9749,13 +9759,13 @@
         <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9763,7 +9773,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>78</v>
@@ -9805,7 +9815,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -9837,10 +9847,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9863,13 +9873,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9918,7 +9928,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9950,13 +9960,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>78</v>
@@ -9981,7 +9991,7 @@
         <v>112</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>198</v>
@@ -10067,10 +10077,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10182,10 +10192,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10297,10 +10307,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10326,13 +10336,13 @@
         <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10340,7 +10350,7 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>78</v>
@@ -10382,7 +10392,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>91</v>
@@ -10414,10 +10424,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10440,13 +10450,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10497,7 +10507,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10529,13 +10539,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
@@ -10560,7 +10570,7 @@
         <v>112</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>198</v>
@@ -10646,10 +10656,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10761,10 +10771,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10876,10 +10886,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10905,13 +10915,13 @@
         <v>133</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10919,7 +10929,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>78</v>
@@ -10961,7 +10971,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>91</v>
@@ -10993,10 +11003,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11019,13 +11029,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11076,7 +11086,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11108,10 +11118,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11137,13 +11147,13 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11151,7 +11161,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -11193,7 +11203,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -11225,10 +11235,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11251,13 +11261,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11308,7 +11318,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11340,19 +11350,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>79</v>
@@ -11370,13 +11380,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11436,7 +11446,7 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>120</v>
@@ -11459,10 +11469,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11574,10 +11584,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11585,7 +11595,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>80</v>
@@ -11689,13 +11699,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>78</v>
@@ -11720,7 +11730,7 @@
         <v>112</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>198</v>
@@ -11806,10 +11816,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11921,10 +11931,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12036,10 +12046,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12065,13 +12075,13 @@
         <v>133</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12079,7 +12089,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>78</v>
@@ -12121,7 +12131,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -12153,10 +12163,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12179,13 +12189,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12212,11 +12222,11 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -12234,7 +12244,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12266,13 +12276,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>78</v>
@@ -12297,7 +12307,7 @@
         <v>112</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>198</v>
@@ -12383,10 +12393,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12498,10 +12508,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12613,10 +12623,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12642,13 +12652,13 @@
         <v>133</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12656,7 +12666,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>78</v>
@@ -12698,7 +12708,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>91</v>
@@ -12730,10 +12740,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12756,13 +12766,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12793,7 +12803,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12811,7 +12821,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12843,13 +12853,13 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>78</v>
@@ -12874,7 +12884,7 @@
         <v>112</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>198</v>
@@ -12960,10 +12970,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13075,10 +13085,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13190,10 +13200,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13219,13 +13229,13 @@
         <v>133</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13233,7 +13243,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>78</v>
@@ -13275,7 +13285,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>91</v>
@@ -13307,10 +13317,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13333,13 +13343,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13390,7 +13400,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13422,13 +13432,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -13453,7 +13463,7 @@
         <v>112</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>198</v>
@@ -13539,10 +13549,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13654,10 +13664,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13769,10 +13779,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13798,13 +13808,13 @@
         <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13812,7 +13822,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>78</v>
@@ -13854,7 +13864,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13886,10 +13896,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13912,13 +13922,13 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13969,7 +13979,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14001,10 +14011,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14030,13 +14040,13 @@
         <v>133</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14044,7 +14054,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -14086,7 +14096,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -14118,10 +14128,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14144,13 +14154,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14201,7 +14211,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14233,19 +14243,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>79</v>
@@ -14263,13 +14273,13 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14329,7 +14339,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>120</v>
@@ -14352,10 +14362,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14467,10 +14477,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14478,7 +14488,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>80</v>
@@ -14582,13 +14592,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>78</v>
@@ -14613,7 +14623,7 @@
         <v>112</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>198</v>
@@ -14699,10 +14709,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14814,10 +14824,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14929,10 +14939,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14958,13 +14968,13 @@
         <v>133</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14972,7 +14982,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>78</v>
@@ -15014,7 +15024,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>91</v>
@@ -15046,10 +15056,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15072,13 +15082,13 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15105,11 +15115,11 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -15127,7 +15137,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15159,13 +15169,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>78</v>
@@ -15190,7 +15200,7 @@
         <v>112</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>198</v>
@@ -15276,10 +15286,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15391,10 +15401,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15506,10 +15516,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15535,13 +15545,13 @@
         <v>133</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15549,7 +15559,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15591,7 +15601,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>91</v>
@@ -15623,10 +15633,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15649,13 +15659,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15682,11 +15692,11 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15704,7 +15714,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15736,13 +15746,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>78</v>
@@ -15767,7 +15777,7 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>198</v>
@@ -15853,10 +15863,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15968,10 +15978,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16083,10 +16093,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16112,13 +16122,13 @@
         <v>133</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16126,7 +16136,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>78</v>
@@ -16168,7 +16178,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>91</v>
@@ -16200,10 +16210,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16226,13 +16236,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16283,7 +16293,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16315,13 +16325,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>78</v>
@@ -16346,7 +16356,7 @@
         <v>112</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>198</v>
@@ -16412,7 +16422,7 @@
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
@@ -16432,10 +16442,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16547,10 +16557,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16662,10 +16672,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16691,13 +16701,13 @@
         <v>133</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16705,7 +16715,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>78</v>
@@ -16747,7 +16757,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>91</v>
@@ -16779,10 +16789,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16805,13 +16815,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16862,7 +16872,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16894,10 +16904,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16923,13 +16933,13 @@
         <v>133</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16937,7 +16947,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>78</v>
@@ -16979,7 +16989,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>91</v>
@@ -17011,10 +17021,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17037,13 +17047,13 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17094,7 +17104,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17126,19 +17136,19 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F122" t="s" s="2">
         <v>79</v>
@@ -17156,13 +17166,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17222,7 +17232,7 @@
         <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>120</v>
@@ -17234,7 +17244,7 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17245,19 +17255,19 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>79</v>
@@ -17275,13 +17285,13 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17347,10 +17357,10 @@
         <v>120</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -17364,10 +17374,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17456,7 +17466,7 @@
         <v>91</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>78</v>
@@ -17479,10 +17489,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17594,10 +17604,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17623,13 +17633,13 @@
         <v>133</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17637,7 +17647,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>78</v>
@@ -17679,7 +17689,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>91</v>
@@ -17711,10 +17721,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17737,13 +17747,13 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17794,7 +17804,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17803,7 +17813,7 @@
         <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>103</v>
@@ -17826,19 +17836,19 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>79</v>
@@ -17856,13 +17866,13 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17922,7 +17932,7 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>120</v>
@@ -17945,10 +17955,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18026,7 +18036,7 @@
         <v>118</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18058,13 +18068,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="B130" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="C130" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18086,10 +18096,10 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>198</v>
@@ -18143,7 +18153,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18152,7 +18162,7 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>120</v>
@@ -18175,10 +18185,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18201,16 +18211,16 @@
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18260,7 +18270,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18275,27 +18285,27 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18321,16 +18331,16 @@
         <v>171</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -18355,13 +18365,13 @@
         <v>78</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>78</v>
@@ -18379,7 +18389,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>91</v>
@@ -18394,27 +18404,27 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18437,19 +18447,19 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18477,10 +18487,10 @@
         <v>175</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>78</v>
@@ -18498,7 +18508,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>91</v>
@@ -18513,27 +18523,27 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18556,19 +18566,19 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18596,10 +18606,10 @@
         <v>161</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -18615,7 +18625,7 @@
         <v>118</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18630,30 +18640,30 @@
         <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>78</v>
@@ -18675,19 +18685,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18697,7 +18707,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>78</v>
@@ -18715,10 +18725,10 @@
         <v>161</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>78</v>
@@ -18736,7 +18746,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18751,27 +18761,27 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18794,19 +18804,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18855,7 +18865,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18873,24 +18883,24 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19002,10 +19012,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19119,10 +19129,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19148,13 +19158,13 @@
         <v>105</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19204,7 +19214,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19213,7 +19223,7 @@
         <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>103</v>
@@ -19236,10 +19246,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19265,13 +19275,13 @@
         <v>133</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19300,10 +19310,10 @@
         <v>153</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>78</v>
@@ -19321,7 +19331,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19353,10 +19363,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19379,16 +19389,16 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19438,7 +19448,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19456,7 +19466,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -19470,10 +19480,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19499,13 +19509,13 @@
         <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19555,7 +19565,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19587,10 +19597,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19613,17 +19623,17 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19672,7 +19682,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19687,27 +19697,27 @@
         <v>103</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19730,19 +19740,19 @@
         <v>92</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -19791,7 +19801,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>91</v>
@@ -19806,27 +19816,27 @@
         <v>103</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19849,17 +19859,17 @@
         <v>92</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19908,7 +19918,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>91</v>
@@ -19923,27 +19933,27 @@
         <v>103</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20055,10 +20065,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20170,13 +20180,13 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>78</v>
@@ -20198,13 +20208,13 @@
         <v>78</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20287,10 +20297,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20316,13 +20326,13 @@
         <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20372,7 +20382,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20381,7 +20391,7 @@
         <v>91</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>103</v>
@@ -20404,10 +20414,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20433,13 +20443,13 @@
         <v>133</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20468,10 +20478,10 @@
         <v>153</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>78</v>
@@ -20489,7 +20499,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20521,10 +20531,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20547,16 +20557,16 @@
         <v>92</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20606,7 +20616,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20624,7 +20634,7 @@
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>78</v>
@@ -20638,10 +20648,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20667,13 +20677,13 @@
         <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20723,7 +20733,7 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20755,10 +20765,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20784,13 +20794,13 @@
         <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20840,7 +20850,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>91</v>
@@ -20858,13 +20868,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -20872,10 +20882,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20901,13 +20911,13 @@
         <v>171</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -20933,13 +20943,13 @@
         <v>78</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>78</v>
@@ -20957,7 +20967,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20975,13 +20985,13 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>78</v>
@@ -20989,10 +20999,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21015,19 +21025,19 @@
         <v>78</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>78</v>
@@ -21064,10 +21074,10 @@
         <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>78</v>
@@ -21076,7 +21086,7 @@
         <v>118</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21094,13 +21104,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21108,10 +21118,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21223,10 +21233,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21340,14 +21350,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21369,16 +21379,16 @@
         <v>112</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21427,7 +21437,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21459,10 +21469,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21488,14 +21498,14 @@
         <v>171</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21520,13 +21530,13 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -21544,7 +21554,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>91</v>
@@ -21562,10 +21572,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>78</v>
@@ -21576,10 +21586,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21602,17 +21612,17 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -21661,7 +21671,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21679,10 +21689,10 @@
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>78</v>
@@ -21693,10 +21703,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21719,17 +21729,17 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -21778,7 +21788,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21796,27 +21806,27 @@
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21838,19 +21848,19 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21899,7 +21909,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21917,13 +21927,13 @@
         <v>78</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>78</v>
@@ -21931,10 +21941,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22046,10 +22056,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22163,14 +22173,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -22192,16 +22202,16 @@
         <v>112</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>78</v>
@@ -22250,7 +22260,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22282,10 +22292,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22311,14 +22321,14 @@
         <v>171</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22328,7 +22338,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22343,13 +22353,13 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
@@ -22367,7 +22377,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>91</v>
@@ -22385,10 +22395,10 @@
         <v>78</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>78</v>
@@ -22399,10 +22409,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22425,17 +22435,17 @@
         <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22484,7 +22494,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22502,10 +22512,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22516,10 +22526,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22542,17 +22552,17 @@
         <v>78</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22601,7 +22611,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22619,27 +22629,27 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -22661,19 +22671,19 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22722,7 +22732,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22740,13 +22750,13 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>78</v>
@@ -22754,10 +22764,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22869,10 +22879,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22986,14 +22996,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -23015,16 +23025,16 @@
         <v>112</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>78</v>
@@ -23073,7 +23083,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23105,10 +23115,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23134,14 +23144,14 @@
         <v>171</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -23151,7 +23161,7 @@
         <v>78</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>78</v>
@@ -23166,13 +23176,13 @@
         <v>78</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>78</v>
@@ -23190,7 +23200,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>91</v>
@@ -23208,10 +23218,10 @@
         <v>78</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>78</v>
@@ -23222,10 +23232,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23248,17 +23258,17 @@
         <v>78</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -23307,7 +23317,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23325,10 +23335,10 @@
         <v>78</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>78</v>
@@ -23339,10 +23349,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23365,17 +23375,17 @@
         <v>78</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>78</v>
@@ -23424,7 +23434,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23442,24 +23452,24 @@
         <v>78</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23482,19 +23492,19 @@
         <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
@@ -23543,7 +23553,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23561,13 +23571,13 @@
         <v>78</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>78</v>
@@ -23575,10 +23585,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23601,16 +23611,16 @@
         <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23648,10 +23658,10 @@
         <v>78</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>78</v>
@@ -23660,7 +23670,7 @@
         <v>118</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23678,13 +23688,13 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>78</v>
@@ -23692,10 +23702,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23807,10 +23817,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23924,14 +23934,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -23953,16 +23963,16 @@
         <v>112</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -24011,7 +24021,7 @@
         <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24043,10 +24053,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24072,13 +24082,13 @@
         <v>171</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -24104,13 +24114,13 @@
         <v>78</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>78</v>
@@ -24128,7 +24138,7 @@
         <v>78</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>91</v>
@@ -24146,13 +24156,13 @@
         <v>78</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>78</v>
@@ -24160,10 +24170,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24186,13 +24196,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24231,17 +24241,17 @@
         <v>78</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC182" s="2"/>
       <c r="AD182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>91</v>
@@ -24259,13 +24269,13 @@
         <v>78</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>78</v>
@@ -24273,13 +24283,13 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D183" t="s" s="2">
         <v>78</v>
@@ -24301,13 +24311,13 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24358,7 +24368,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>91</v>
@@ -24376,13 +24386,13 @@
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>78</v>
@@ -24390,10 +24400,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24505,10 +24515,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24622,10 +24632,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24651,16 +24661,16 @@
         <v>171</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>78</v>
@@ -24685,13 +24695,13 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
@@ -24709,7 +24719,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24727,7 +24737,7 @@
         <v>78</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>78</v>
@@ -24741,10 +24751,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24767,19 +24777,19 @@
         <v>92</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24807,10 +24817,10 @@
         <v>153</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>78</v>
@@ -24828,7 +24838,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24846,7 +24856,7 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>78</v>
@@ -24860,10 +24870,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24889,16 +24899,16 @@
         <v>133</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24911,7 +24921,7 @@
         <v>78</v>
       </c>
       <c r="T188" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="U188" t="s" s="2">
         <v>78</v>
@@ -24947,7 +24957,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24965,7 +24975,7 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>78</v>
@@ -24979,10 +24989,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25008,13 +25018,13 @@
         <v>105</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -25028,7 +25038,7 @@
         <v>78</v>
       </c>
       <c r="T189" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U189" t="s" s="2">
         <v>78</v>
@@ -25064,7 +25074,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25082,7 +25092,7 @@
         <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>78</v>
@@ -25096,10 +25106,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25122,13 +25132,13 @@
         <v>92</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -25179,7 +25189,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25197,7 +25207,7 @@
         <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>78</v>
@@ -25211,10 +25221,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25237,16 +25247,16 @@
         <v>92</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -25296,7 +25306,7 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25314,7 +25324,7 @@
         <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>78</v>
@@ -25328,13 +25338,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25356,16 +25366,16 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -25415,7 +25425,7 @@
         <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25433,13 +25443,13 @@
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>78</v>
@@ -25447,10 +25457,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25562,10 +25572,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25679,14 +25689,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -25708,16 +25718,16 @@
         <v>112</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -25766,7 +25776,7 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -25798,10 +25808,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25827,13 +25837,13 @@
         <v>171</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -25844,7 +25854,7 @@
         <v>78</v>
       </c>
       <c r="S196" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="T196" t="s" s="2">
         <v>78</v>
@@ -25859,13 +25869,13 @@
         <v>78</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>78</v>
@@ -25883,7 +25893,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>91</v>
@@ -25901,13 +25911,13 @@
         <v>78</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25915,10 +25925,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25941,13 +25951,13 @@
         <v>78</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -25986,17 +25996,17 @@
         <v>78</v>
       </c>
       <c r="AB197" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC197" s="2"/>
       <c r="AD197" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE197" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>91</v>
@@ -26014,13 +26024,13 @@
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -26028,13 +26038,13 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>78</v>
@@ -26056,13 +26066,13 @@
         <v>78</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -26113,7 +26123,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>91</v>
@@ -26131,13 +26141,13 @@
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>78</v>
@@ -26145,10 +26155,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26260,10 +26270,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26377,10 +26387,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26406,16 +26416,16 @@
         <v>171</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26440,13 +26450,13 @@
         <v>78</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>78</v>
@@ -26464,7 +26474,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26482,7 +26492,7 @@
         <v>78</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>78</v>
@@ -26496,10 +26506,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26522,19 +26532,19 @@
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26562,10 +26572,10 @@
         <v>153</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>78</v>
@@ -26583,7 +26593,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26601,7 +26611,7 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>78</v>
@@ -26615,10 +26625,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26644,16 +26654,16 @@
         <v>133</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26666,7 +26676,7 @@
         <v>78</v>
       </c>
       <c r="T203" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="U203" t="s" s="2">
         <v>78</v>
@@ -26702,7 +26712,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26720,7 +26730,7 @@
         <v>78</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>78</v>
@@ -26734,10 +26744,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26763,13 +26773,13 @@
         <v>105</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -26783,7 +26793,7 @@
         <v>78</v>
       </c>
       <c r="T204" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U204" t="s" s="2">
         <v>78</v>
@@ -26819,7 +26829,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -26837,7 +26847,7 @@
         <v>78</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>78</v>
@@ -26851,10 +26861,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26877,13 +26887,13 @@
         <v>92</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26934,7 +26944,7 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -26952,7 +26962,7 @@
         <v>78</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>78</v>
@@ -26966,10 +26976,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26992,16 +27002,16 @@
         <v>92</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27051,7 +27061,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27069,7 +27079,7 @@
         <v>78</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>78</v>
@@ -27083,13 +27093,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>78</v>
@@ -27111,16 +27121,16 @@
         <v>78</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27170,7 +27180,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27188,13 +27198,13 @@
         <v>78</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27202,10 +27212,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27317,10 +27327,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27434,14 +27444,14 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -27463,16 +27473,16 @@
         <v>112</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N210" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27521,7 +27531,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27553,10 +27563,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27582,13 +27592,13 @@
         <v>171</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -27599,7 +27609,7 @@
         <v>78</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>78</v>
@@ -27614,13 +27624,13 @@
         <v>78</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27638,7 +27648,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>91</v>
@@ -27656,13 +27666,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27670,10 +27680,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27696,13 +27706,13 @@
         <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -27741,17 +27751,17 @@
         <v>78</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC212" s="2"/>
       <c r="AD212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>91</v>
@@ -27769,13 +27779,13 @@
         <v>78</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>78</v>
@@ -27783,13 +27793,13 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>78</v>
@@ -27811,13 +27821,13 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -27868,7 +27878,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>91</v>
@@ -27886,13 +27896,13 @@
         <v>78</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -27900,10 +27910,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28015,10 +28025,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28132,10 +28142,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28161,16 +28171,16 @@
         <v>171</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28195,13 +28205,13 @@
         <v>78</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>78</v>
@@ -28219,7 +28229,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28237,7 +28247,7 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>78</v>
@@ -28251,10 +28261,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28277,19 +28287,19 @@
         <v>92</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28317,10 +28327,10 @@
         <v>153</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>78</v>
@@ -28338,7 +28348,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28356,7 +28366,7 @@
         <v>78</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>78</v>
@@ -28370,10 +28380,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28399,16 +28409,16 @@
         <v>133</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>78</v>
@@ -28421,7 +28431,7 @@
         <v>78</v>
       </c>
       <c r="T218" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="U218" t="s" s="2">
         <v>78</v>
@@ -28457,7 +28467,7 @@
         <v>78</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28475,7 +28485,7 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>78</v>
@@ -28489,10 +28499,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28518,13 +28528,13 @@
         <v>105</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -28538,7 +28548,7 @@
         <v>78</v>
       </c>
       <c r="T219" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U219" t="s" s="2">
         <v>78</v>
@@ -28574,7 +28584,7 @@
         <v>78</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>79</v>
@@ -28592,7 +28602,7 @@
         <v>78</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>78</v>
@@ -28606,10 +28616,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28632,13 +28642,13 @@
         <v>92</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -28689,7 +28699,7 @@
         <v>78</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>79</v>
@@ -28707,7 +28717,7 @@
         <v>78</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>78</v>
@@ -28721,10 +28731,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28747,16 +28757,16 @@
         <v>92</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
@@ -28806,7 +28816,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -28824,7 +28834,7 @@
         <v>78</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>78</v>
@@ -28838,13 +28848,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>78</v>
@@ -28866,16 +28876,16 @@
         <v>78</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
@@ -28925,7 +28935,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -28943,13 +28953,13 @@
         <v>78</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>78</v>
@@ -28957,10 +28967,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29072,10 +29082,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29189,14 +29199,14 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
@@ -29218,16 +29228,16 @@
         <v>112</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N225" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>78</v>
@@ -29276,7 +29286,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29308,10 +29318,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29337,13 +29347,13 @@
         <v>171</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -29354,7 +29364,7 @@
         <v>78</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>78</v>
@@ -29369,13 +29379,13 @@
         <v>78</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>78</v>
@@ -29393,7 +29403,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>91</v>
@@ -29411,13 +29421,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29425,10 +29435,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29451,13 +29461,13 @@
         <v>78</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -29496,7 +29506,7 @@
         <v>78</v>
       </c>
       <c r="AB227" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AC227" s="2"/>
       <c r="AD227" t="s" s="2">
@@ -29506,7 +29516,7 @@
         <v>118</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>91</v>
@@ -29524,13 +29534,13 @@
         <v>78</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM227" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>78</v>
@@ -29538,13 +29548,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>78</v>
@@ -29566,13 +29576,13 @@
         <v>78</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -29623,7 +29633,7 @@
         <v>78</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>91</v>
@@ -29641,13 +29651,13 @@
         <v>78</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AM228" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>78</v>
@@ -29655,10 +29665,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29681,19 +29691,19 @@
         <v>92</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>78</v>
@@ -29740,7 +29750,7 @@
         <v>118</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>79</v>
@@ -29758,13 +29768,13 @@
         <v>78</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AM229" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>78</v>
@@ -29772,10 +29782,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29887,10 +29897,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30000,13 +30010,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30028,13 +30038,13 @@
         <v>78</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -30094,7 +30104,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>120</v>
@@ -30117,14 +30127,14 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
@@ -30146,16 +30156,16 @@
         <v>112</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N233" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>78</v>
@@ -30204,7 +30214,7 @@
         <v>78</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>79</v>
@@ -30236,10 +30246,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30262,16 +30272,16 @@
         <v>92</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
@@ -30300,10 +30310,10 @@
         <v>161</v>
       </c>
       <c r="Y234" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>78</v>
@@ -30321,7 +30331,7 @@
         <v>78</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>79</v>
@@ -30339,13 +30349,13 @@
         <v>78</v>
       </c>
       <c r="AL234" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM234" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>78</v>
@@ -30353,10 +30363,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30379,13 +30389,13 @@
         <v>92</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -30436,7 +30446,7 @@
         <v>78</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>79</v>
@@ -30454,13 +30464,13 @@
         <v>78</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>78</v>
@@ -30468,10 +30478,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30494,13 +30504,13 @@
         <v>92</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -30551,7 +30561,7 @@
         <v>78</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>79</v>
@@ -30569,7 +30579,7 @@
         <v>78</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>109</v>
@@ -30583,13 +30593,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30611,19 +30621,19 @@
         <v>92</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>78</v>
@@ -30672,7 +30682,7 @@
         <v>78</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>79</v>
@@ -30690,13 +30700,13 @@
         <v>78</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AN237" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AO237" t="s" s="2">
         <v>78</v>
@@ -30704,10 +30714,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30819,10 +30829,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -30932,13 +30942,13 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D240" t="s" s="2">
         <v>78</v>
@@ -30960,13 +30970,13 @@
         <v>78</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -31026,7 +31036,7 @@
         <v>80</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>120</v>
@@ -31049,14 +31059,14 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -31078,16 +31088,16 @@
         <v>112</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N241" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>78</v>
@@ -31136,7 +31146,7 @@
         <v>78</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>79</v>
@@ -31168,10 +31178,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31194,16 +31204,16 @@
         <v>92</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
@@ -31232,10 +31242,10 @@
         <v>161</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>78</v>
@@ -31253,7 +31263,7 @@
         <v>78</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>79</v>
@@ -31271,13 +31281,13 @@
         <v>78</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN242" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO242" t="s" s="2">
         <v>78</v>
@@ -31285,10 +31295,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31311,13 +31321,13 @@
         <v>92</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -31368,7 +31378,7 @@
         <v>78</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>79</v>
@@ -31386,13 +31396,13 @@
         <v>78</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN243" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AO243" t="s" s="2">
         <v>78</v>
@@ -31400,10 +31410,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31426,13 +31436,13 @@
         <v>92</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -31483,7 +31493,7 @@
         <v>78</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>79</v>
@@ -31501,7 +31511,7 @@
         <v>78</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AM244" t="s" s="2">
         <v>109</v>
@@ -31515,10 +31525,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31541,13 +31551,13 @@
         <v>78</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -31598,7 +31608,7 @@
         <v>78</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>79</v>
@@ -31610,16 +31620,16 @@
         <v>78</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AK245" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>78</v>
@@ -31630,10 +31640,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31745,10 +31755,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -31858,13 +31868,13 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D248" t="s" s="2">
         <v>78</v>
@@ -31886,13 +31896,13 @@
         <v>78</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -31952,7 +31962,7 @@
         <v>80</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>120</v>
@@ -31975,14 +31985,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32004,16 +32014,16 @@
         <v>112</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O249" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>78</v>
@@ -32062,7 +32072,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32094,14 +32104,14 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
@@ -32123,16 +32133,16 @@
         <v>105</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="O250" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32181,7 +32191,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32199,10 +32209,10 @@
         <v>78</v>
       </c>
       <c r="AL250" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32213,10 +32223,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32239,19 +32249,19 @@
         <v>78</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>78</v>
@@ -32276,11 +32286,11 @@
         <v>78</v>
       </c>
       <c r="X251" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32298,7 +32308,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>79</v>
@@ -32316,10 +32326,10 @@
         <v>78</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN251" t="s" s="2">
         <v>78</v>
@@ -32330,10 +32340,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32356,17 +32366,17 @@
         <v>78</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>78</v>
@@ -32415,7 +32425,7 @@
         <v>78</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>79</v>
@@ -32433,24 +32443,24 @@
         <v>78</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AM252" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN252" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO252" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32473,16 +32483,16 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
@@ -32532,7 +32542,7 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>79</v>
@@ -32553,7 +32563,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32564,10 +32574,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32593,13 +32603,13 @@
         <v>182</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="O254" s="2"/>
       <c r="P254" t="s" s="2">
@@ -32649,7 +32659,7 @@
         <v>78</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>79</v>
@@ -32658,7 +32668,7 @@
         <v>91</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>103</v>
@@ -32667,10 +32677,10 @@
         <v>78</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>78</v>
@@ -32681,10 +32691,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -32710,16 +32720,16 @@
         <v>171</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>78</v>
@@ -32744,13 +32754,13 @@
         <v>78</v>
       </c>
       <c r="X255" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y255" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="Z255" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -32768,7 +32778,7 @@
         <v>78</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>79</v>
@@ -32786,7 +32796,7 @@
         <v>78</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AM255" t="s" s="2">
         <v>109</v>
@@ -32795,15 +32805,15 @@
         <v>78</v>
       </c>
       <c r="AO255" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -32826,19 +32836,19 @@
         <v>78</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="P256" t="s" s="2">
         <v>78</v>
@@ -32866,10 +32876,10 @@
         <v>175</v>
       </c>
       <c r="Y256" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="Z256" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -32887,7 +32897,7 @@
         <v>78</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>79</v>
@@ -32905,7 +32915,7 @@
         <v>78</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AM256" t="s" s="2">
         <v>109</v>
@@ -32919,10 +32929,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -32945,16 +32955,16 @@
         <v>78</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -33004,7 +33014,7 @@
         <v>78</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>79</v>
@@ -33013,7 +33023,7 @@
         <v>80</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>103</v>
@@ -33022,10 +33032,10 @@
         <v>78</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AN257" t="s" s="2">
         <v>78</v>
@@ -33036,10 +33046,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33062,19 +33072,19 @@
         <v>78</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33102,10 +33112,10 @@
         <v>175</v>
       </c>
       <c r="Y258" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="Z258" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AA258" t="s" s="2">
         <v>78</v>
@@ -33123,7 +33133,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33132,7 +33142,7 @@
         <v>91</v>
       </c>
       <c r="AI258" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AJ258" t="s" s="2">
         <v>103</v>
@@ -33141,7 +33151,7 @@
         <v>78</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>109</v>
@@ -33155,10 +33165,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33184,13 +33194,13 @@
         <v>81</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
@@ -33240,7 +33250,7 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>79</v>
@@ -33249,7 +33259,7 @@
         <v>80</v>
       </c>
       <c r="AI259" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AJ259" t="s" s="2">
         <v>103</v>
@@ -33258,10 +33268,10 @@
         <v>78</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AN259" t="s" s="2">
         <v>78</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
